--- a/templates/students_template.xlsx
+++ b/templates/students_template.xlsx
@@ -436,11 +436,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,11 +455,16 @@
           <t>Student Name</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Student Email</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t># Legend: one row per student. Contact SF ID must be unique. Rows starting with # are ignored.</t>
+          <t># Legend: one row per student. Every column is required — all three are exported. Contact SF ID must be unique. Student Email must be a real address (name@example.com). Rows starting with # are ignored.</t>
         </is>
       </c>
     </row>
@@ -471,6 +477,11 @@
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Jane Doe</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>jane.doe@example.com</t>
         </is>
       </c>
     </row>

--- a/templates/students_template.xlsx
+++ b/templates/students_template.xlsx
@@ -436,12 +436,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,11 +461,16 @@
           <t>Student Email</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Class Block</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t># Legend: one row per student. Every column is required — all three are exported. Contact SF ID must be unique. Student Email must be a real address (name@example.com). Rows starting with # are ignored.</t>
+          <t># Legend: one row per student. Every column is required. Contact SF ID must be unique. Student Email must be a real address (name@example.com). Class Block must match a class block in the class schedule exactly — one block per student, never two. Rows starting with # are ignored.</t>
         </is>
       </c>
     </row>
@@ -482,6 +488,33 @@
       <c r="C3" s="3" t="inlineStr">
         <is>
           <t>jane.doe@example.com</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Block A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>0031t00000FgHiJ</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Sam Patel</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>sam.patel@example.com</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Block B</t>
         </is>
       </c>
     </row>
